--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>1015543.88</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>967753.8100000001</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>962259.6899999999</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>856031.5600000001</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>848713.38</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>712174.1899999999</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>653121.0600000001</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>640893.9399999999</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>608126.6899999999</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>558202.0600000001</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>520258.03</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>505286.38</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>487496.72</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>463080.38</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>461524.31</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>459116.5</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>451923.09</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>448412.19</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>446942.47</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>443246.19</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>416749.75</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>409760.12</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>408933.69</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>405932.75</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>403801.47</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>392352.44</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>387252.56</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>383718.5</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>382117.84</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>381947.84</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>371511.12</v>
       </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>369292.28</v>
       </c>
-      <c r="F33" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -812,9 +711,6 @@
       <c r="B34">
         <v>364957.44</v>
       </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -825,9 +721,6 @@
       <c r="B35">
         <v>350768.75</v>
       </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -838,9 +731,6 @@
       <c r="B36">
         <v>335872.31</v>
       </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -851,9 +741,6 @@
       <c r="B37">
         <v>335464.53</v>
       </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -864,9 +751,6 @@
       <c r="B38">
         <v>334567.12</v>
       </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -877,9 +761,6 @@
       <c r="B39">
         <v>328957.22</v>
       </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -890,9 +771,6 @@
       <c r="B40">
         <v>319411.72</v>
       </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -903,9 +781,6 @@
       <c r="B41">
         <v>317556.84</v>
       </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -916,9 +791,6 @@
       <c r="B42">
         <v>304401.69</v>
       </c>
-      <c r="F42" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -929,9 +801,6 @@
       <c r="B43">
         <v>303825.31</v>
       </c>
-      <c r="F43" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -942,9 +811,6 @@
       <c r="B44">
         <v>295409.34</v>
       </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -955,9 +821,6 @@
       <c r="B45">
         <v>288901.03</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -968,9 +831,6 @@
       <c r="B46">
         <v>286766.53</v>
       </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -981,9 +841,6 @@
       <c r="B47">
         <v>286410.47</v>
       </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -994,9 +851,6 @@
       <c r="B48">
         <v>283090.53</v>
       </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1007,9 +861,6 @@
       <c r="B49">
         <v>280565.25</v>
       </c>
-      <c r="F49" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1020,9 +871,6 @@
       <c r="B50">
         <v>271989.5</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1033,9 +881,6 @@
       <c r="B51">
         <v>267090.22</v>
       </c>
-      <c r="F51" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1046,9 +891,6 @@
       <c r="B52">
         <v>247375.78</v>
       </c>
-      <c r="F52" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1058,9 +900,6 @@
       </c>
       <c r="B53">
         <v>223357.52</v>
-      </c>
-      <c r="F53" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>1015543.88</v>
       </c>
+      <c r="C2">
+        <v>919018.0600000001</v>
+      </c>
+      <c r="D2">
+        <v>96525.81999999995</v>
+      </c>
+      <c r="E2">
+        <v>10.50314723956567</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>967753.8100000001</v>
       </c>
+      <c r="C3">
+        <v>866389.5600000001</v>
+      </c>
+      <c r="D3">
+        <v>101364.25</v>
+      </c>
+      <c r="E3">
+        <v>11.69961581716197</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>962259.6899999999</v>
       </c>
+      <c r="C4">
+        <v>867524.9399999999</v>
+      </c>
+      <c r="D4">
+        <v>94734.75</v>
+      </c>
+      <c r="E4">
+        <v>10.92011833112256</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>856031.5600000001</v>
       </c>
+      <c r="C5">
+        <v>753554.62</v>
+      </c>
+      <c r="D5">
+        <v>102476.9400000001</v>
+      </c>
+      <c r="E5">
+        <v>13.59913897150549</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>848713.38</v>
       </c>
+      <c r="C6">
+        <v>754320</v>
+      </c>
+      <c r="D6">
+        <v>94393.38</v>
+      </c>
+      <c r="E6">
+        <v>12.51370505886096</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>712174.1899999999</v>
       </c>
+      <c r="C7">
+        <v>629392.62</v>
+      </c>
+      <c r="D7">
+        <v>82781.56999999995</v>
+      </c>
+      <c r="E7">
+        <v>13.15261211674201</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>653121.0600000001</v>
       </c>
+      <c r="C8">
+        <v>582424.9399999999</v>
+      </c>
+      <c r="D8">
+        <v>70696.12000000011</v>
+      </c>
+      <c r="E8">
+        <v>12.13823707480661</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>640893.9399999999</v>
       </c>
+      <c r="C9">
+        <v>554210.4399999999</v>
+      </c>
+      <c r="D9">
+        <v>86683.5</v>
+      </c>
+      <c r="E9">
+        <v>15.64089987189703</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>608126.6899999999</v>
       </c>
+      <c r="C10">
+        <v>538928.6899999999</v>
+      </c>
+      <c r="D10">
+        <v>69198</v>
+      </c>
+      <c r="E10">
+        <v>12.83991765218511</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,6 +562,15 @@
       <c r="B11">
         <v>558202.0600000001</v>
       </c>
+      <c r="C11">
+        <v>518707.31</v>
+      </c>
+      <c r="D11">
+        <v>39494.75000000006</v>
+      </c>
+      <c r="E11">
+        <v>7.614072375421133</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -501,6 +591,15 @@
       <c r="B13">
         <v>505286.38</v>
       </c>
+      <c r="C13">
+        <v>437465.06</v>
+      </c>
+      <c r="D13">
+        <v>67821.32000000001</v>
+      </c>
+      <c r="E13">
+        <v>15.50325413417017</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,395 +610,774 @@
       <c r="B14">
         <v>487496.72</v>
       </c>
+      <c r="C14">
+        <v>421659.75</v>
+      </c>
+      <c r="D14">
+        <v>65836.96999999997</v>
+      </c>
+      <c r="E14">
+        <v>15.61376678708366</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B15">
-        <v>463080.38</v>
+        <v>477649.97</v>
+      </c>
+      <c r="C15">
+        <v>420091.09</v>
+      </c>
+      <c r="D15">
+        <v>57558.87999999995</v>
+      </c>
+      <c r="E15">
+        <v>13.70152363859942</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="B16">
-        <v>461524.31</v>
+        <v>463080.38</v>
+      </c>
+      <c r="C16">
+        <v>403190.38</v>
+      </c>
+      <c r="D16">
+        <v>59890</v>
+      </c>
+      <c r="E16">
+        <v>14.85402503899027</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="B17">
-        <v>459116.5</v>
+        <v>461524.31</v>
+      </c>
+      <c r="C17">
+        <v>400012.25</v>
+      </c>
+      <c r="D17">
+        <v>61512.06</v>
+      </c>
+      <c r="E17">
+        <v>15.37754406271308</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
+          <t>Quilicura</t>
         </is>
       </c>
       <c r="B18">
-        <v>451923.09</v>
+        <v>459116.5</v>
+      </c>
+      <c r="C18">
+        <v>405604.38</v>
+      </c>
+      <c r="D18">
+        <v>53512.12</v>
+      </c>
+      <c r="E18">
+        <v>13.19318100065883</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
+          <t>Padre Hurtado</t>
         </is>
       </c>
       <c r="B19">
-        <v>448412.19</v>
+        <v>451923.09</v>
+      </c>
+      <c r="C19">
+        <v>380988.41</v>
+      </c>
+      <c r="D19">
+        <v>70934.68000000005</v>
+      </c>
+      <c r="E19">
+        <v>18.61859262332943</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Calera de Tango</t>
         </is>
       </c>
       <c r="B20">
-        <v>446942.47</v>
+        <v>448412.19</v>
+      </c>
+      <c r="C20">
+        <v>363685.88</v>
+      </c>
+      <c r="D20">
+        <v>84726.31</v>
+      </c>
+      <c r="E20">
+        <v>23.29656295702214</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="B21">
-        <v>443246.19</v>
+        <v>446942.47</v>
+      </c>
+      <c r="C21">
+        <v>392694.41</v>
+      </c>
+      <c r="D21">
+        <v>54248.06</v>
+      </c>
+      <c r="E21">
+        <v>13.81431938386899</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Pirque</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="B22">
-        <v>416749.75</v>
+        <v>443246.19</v>
+      </c>
+      <c r="C22">
+        <v>382639.12</v>
+      </c>
+      <c r="D22">
+        <v>60607.07000000001</v>
+      </c>
+      <c r="E22">
+        <v>15.83922469819605</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Pirque</t>
         </is>
       </c>
       <c r="B23">
-        <v>409760.12</v>
+        <v>416749.75</v>
+      </c>
+      <c r="C23">
+        <v>361396.75</v>
+      </c>
+      <c r="D23">
+        <v>55353</v>
+      </c>
+      <c r="E23">
+        <v>15.31640779835457</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="B24">
-        <v>408933.69</v>
+        <v>409760.12</v>
+      </c>
+      <c r="C24">
+        <v>356517.03</v>
+      </c>
+      <c r="D24">
+        <v>53243.08999999997</v>
+      </c>
+      <c r="E24">
+        <v>14.93423469840978</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="B25">
-        <v>405932.75</v>
+        <v>408933.69</v>
+      </c>
+      <c r="C25">
+        <v>357578.25</v>
+      </c>
+      <c r="D25">
+        <v>51355.44</v>
+      </c>
+      <c r="E25">
+        <v>14.36201446816185</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Pudahuel</t>
         </is>
       </c>
       <c r="B26">
-        <v>403801.47</v>
+        <v>405932.75</v>
+      </c>
+      <c r="C26">
+        <v>356652.28</v>
+      </c>
+      <c r="D26">
+        <v>49280.46999999997</v>
+      </c>
+      <c r="E26">
+        <v>13.81751155495206</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alhué</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="B27">
-        <v>392352.44</v>
+        <v>403801.47</v>
+      </c>
+      <c r="C27">
+        <v>351663.81</v>
+      </c>
+      <c r="D27">
+        <v>52137.65999999997</v>
+      </c>
+      <c r="E27">
+        <v>14.825995316379</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Alhué</t>
         </is>
       </c>
       <c r="B28">
-        <v>387252.56</v>
+        <v>392352.44</v>
+      </c>
+      <c r="C28">
+        <v>334217.44</v>
+      </c>
+      <c r="D28">
+        <v>58135</v>
+      </c>
+      <c r="E28">
+        <v>17.39436457893999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="B29">
-        <v>383718.5</v>
+        <v>387252.56</v>
+      </c>
+      <c r="C29">
+        <v>341532.94</v>
+      </c>
+      <c r="D29">
+        <v>45719.62</v>
+      </c>
+      <c r="E29">
+        <v>13.3865916417901</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="B30">
-        <v>382117.84</v>
+        <v>383718.5</v>
+      </c>
+      <c r="C30">
+        <v>328538.94</v>
+      </c>
+      <c r="D30">
+        <v>55179.56</v>
+      </c>
+      <c r="E30">
+        <v>16.79543983431613</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Estación Central</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="B31">
-        <v>381947.84</v>
+        <v>382117.84</v>
+      </c>
+      <c r="C31">
+        <v>331958.75</v>
+      </c>
+      <c r="D31">
+        <v>50159.09000000003</v>
+      </c>
+      <c r="E31">
+        <v>15.1100370151412</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="B32">
-        <v>371511.12</v>
+        <v>381947.84</v>
+      </c>
+      <c r="C32">
+        <v>341788.88</v>
+      </c>
+      <c r="D32">
+        <v>40158.96000000002</v>
+      </c>
+      <c r="E32">
+        <v>11.74963913395897</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
+          <t>Quinta Normal</t>
         </is>
       </c>
       <c r="B33">
-        <v>369292.28</v>
+        <v>371511.12</v>
+      </c>
+      <c r="C33">
+        <v>328408.38</v>
+      </c>
+      <c r="D33">
+        <v>43102.73999999999</v>
+      </c>
+      <c r="E33">
+        <v>13.12473816898338</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>San José de Maipo</t>
         </is>
       </c>
       <c r="B34">
-        <v>364957.44</v>
+        <v>369292.28</v>
+      </c>
+      <c r="C34">
+        <v>321533.59</v>
+      </c>
+      <c r="D34">
+        <v>47758.69</v>
+      </c>
+      <c r="E34">
+        <v>14.85340614024184</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="B35">
-        <v>350768.75</v>
+        <v>364957.44</v>
+      </c>
+      <c r="C35">
+        <v>320160.34</v>
+      </c>
+      <c r="D35">
+        <v>44797.09999999998</v>
+      </c>
+      <c r="E35">
+        <v>13.99208284199098</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>Isla de Maipo</t>
         </is>
       </c>
       <c r="B36">
-        <v>335872.31</v>
+        <v>350768.75</v>
+      </c>
+      <c r="C36">
+        <v>298653.69</v>
+      </c>
+      <c r="D36">
+        <v>52115.06</v>
+      </c>
+      <c r="E36">
+        <v>17.44999701828562</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Renca</t>
         </is>
       </c>
       <c r="B37">
-        <v>335464.53</v>
+        <v>335872.31</v>
+      </c>
+      <c r="C37">
+        <v>288504.44</v>
+      </c>
+      <c r="D37">
+        <v>47367.87</v>
+      </c>
+      <c r="E37">
+        <v>16.41841976504763</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="B38">
-        <v>334567.12</v>
+        <v>335464.53</v>
+      </c>
+      <c r="C38">
+        <v>289011.56</v>
+      </c>
+      <c r="D38">
+        <v>46452.97000000003</v>
+      </c>
+      <c r="E38">
+        <v>16.07304911955772</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Curacaví</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="B39">
-        <v>328957.22</v>
+        <v>334567.12</v>
+      </c>
+      <c r="C39">
+        <v>286722.88</v>
+      </c>
+      <c r="D39">
+        <v>47844.23999999999</v>
+      </c>
+      <c r="E39">
+        <v>16.68657904105875</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Conchalí</t>
+          <t>Curacaví</t>
         </is>
       </c>
       <c r="B40">
-        <v>319411.72</v>
+        <v>328957.22</v>
+      </c>
+      <c r="C40">
+        <v>275990</v>
+      </c>
+      <c r="D40">
+        <v>52967.21999999997</v>
+      </c>
+      <c r="E40">
+        <v>19.19171709119896</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Paine</t>
+          <t>Conchalí</t>
         </is>
       </c>
       <c r="B41">
-        <v>317556.84</v>
+        <v>319411.72</v>
+      </c>
+      <c r="C41">
+        <v>273882.34</v>
+      </c>
+      <c r="D41">
+        <v>45529.37999999995</v>
+      </c>
+      <c r="E41">
+        <v>16.62370052775215</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>El Monte</t>
+          <t>Paine</t>
         </is>
       </c>
       <c r="B42">
-        <v>304401.69</v>
+        <v>317556.84</v>
+      </c>
+      <c r="C42">
+        <v>273518.28</v>
+      </c>
+      <c r="D42">
+        <v>44038.56</v>
+      </c>
+      <c r="E42">
+        <v>16.10077395923957</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
+          <t>El Monte</t>
         </is>
       </c>
       <c r="B43">
-        <v>303825.31</v>
+        <v>304401.69</v>
+      </c>
+      <c r="C43">
+        <v>260922.02</v>
+      </c>
+      <c r="D43">
+        <v>43479.67000000001</v>
+      </c>
+      <c r="E43">
+        <v>16.66385612069077</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>María Pinto</t>
+          <t>Lo Prado</t>
         </is>
       </c>
       <c r="B44">
-        <v>295409.34</v>
+        <v>303825.31</v>
+      </c>
+      <c r="C44">
+        <v>263142.03</v>
+      </c>
+      <c r="D44">
+        <v>40683.27999999997</v>
+      </c>
+      <c r="E44">
+        <v>15.46057845643281</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>María Pinto</t>
         </is>
       </c>
       <c r="B45">
-        <v>288901.03</v>
+        <v>295409.34</v>
+      </c>
+      <c r="C45">
+        <v>246894.33</v>
+      </c>
+      <c r="D45">
+        <v>48515.01000000004</v>
+      </c>
+      <c r="E45">
+        <v>19.65011104143219</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>El Bosque</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="B46">
-        <v>286766.53</v>
+        <v>288901.03</v>
+      </c>
+      <c r="C46">
+        <v>249322.14</v>
+      </c>
+      <c r="D46">
+        <v>39578.89000000001</v>
+      </c>
+      <c r="E46">
+        <v>15.87459902277431</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
+          <t>El Bosque</t>
         </is>
       </c>
       <c r="B47">
-        <v>286410.47</v>
+        <v>286766.53</v>
+      </c>
+      <c r="C47">
+        <v>246674.8</v>
+      </c>
+      <c r="D47">
+        <v>40091.73000000004</v>
+      </c>
+      <c r="E47">
+        <v>16.25286814867186</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>La Granja</t>
+          <t>Pedro Aguirre Cerda</t>
         </is>
       </c>
       <c r="B48">
-        <v>283090.53</v>
+        <v>286410.47</v>
+      </c>
+      <c r="C48">
+        <v>243612.08</v>
+      </c>
+      <c r="D48">
+        <v>42798.38999999998</v>
+      </c>
+      <c r="E48">
+        <v>17.5682544149699</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>La Granja</t>
         </is>
       </c>
       <c r="B49">
-        <v>280565.25</v>
+        <v>283090.53</v>
+      </c>
+      <c r="C49">
+        <v>240645.33</v>
+      </c>
+      <c r="D49">
+        <v>42445.20000000004</v>
+      </c>
+      <c r="E49">
+        <v>17.63807342531851</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="B50">
-        <v>271989.5</v>
+        <v>280565.25</v>
+      </c>
+      <c r="C50">
+        <v>234890.59</v>
+      </c>
+      <c r="D50">
+        <v>45674.66</v>
+      </c>
+      <c r="E50">
+        <v>19.44507866407079</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>Lo Espejo</t>
         </is>
       </c>
       <c r="B51">
-        <v>267090.22</v>
+        <v>271989.5</v>
+      </c>
+      <c r="C51">
+        <v>222282.17</v>
+      </c>
+      <c r="D51">
+        <v>49707.32999999999</v>
+      </c>
+      <c r="E51">
+        <v>22.3622659433278</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>La Pintana</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="B52">
-        <v>247375.78</v>
+        <v>267090.22</v>
+      </c>
+      <c r="C52">
+        <v>225400.12</v>
+      </c>
+      <c r="D52">
+        <v>41690.09999999998</v>
+      </c>
+      <c r="E52">
+        <v>18.49604161701421</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>La Pintana</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>247375.78</v>
+      </c>
+      <c r="C53">
+        <v>209821.86</v>
+      </c>
+      <c r="D53">
+        <v>37553.92000000001</v>
+      </c>
+      <c r="E53">
+        <v>17.89800166674722</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>San Pedro</t>
         </is>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>223357.52</v>
+      </c>
+      <c r="C54">
+        <v>182249</v>
+      </c>
+      <c r="D54">
+        <v>41108.51999999999</v>
+      </c>
+      <c r="E54">
+        <v>22.55623899170913</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
+++ b/output/laminas_comunales/comunal_i_ingr_mean_a_2022_metropolitana.xlsx
@@ -1387,7 +1387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1396,530 +1396,369 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alhué</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>392352.44</v>
+          <t>San Joaquín</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>443246.19</v>
+          <t>San Miguel</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera de Tango</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>448412.19</v>
+          <t>San Ramón</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>383718.5</v>
+          <t>Independencia</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>280565.25</v>
+          <t>La Cisterna</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colina</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>640893.9399999999</v>
+          <t>Peñalolén</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conchalí</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>319411.72</v>
+          <t>Providencia</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Curacaví</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>328957.22</v>
+          <t>La Reina</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Bosque</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>286766.53</v>
+          <t>Calera de Tango</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Monte</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>304401.69</v>
+          <t>Colina</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Estación Central</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>381947.84</v>
+          <t>Santiago</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>608126.6899999999</v>
+          <t>Lampa</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Independencia</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>387252.56</v>
+          <t>Pirque</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Isla de Maipo</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>350768.75</v>
+          <t>Puente Alto</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>409760.12</v>
+          <t>Huechuraba</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>La Florida</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>463080.38</v>
+          <t>San Bernardo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Granja</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>283090.53</v>
+          <t>Curacaví</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>La Pintana</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>247375.78</v>
+          <t>María Pinto</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>La Reina</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>712174.1899999999</v>
+          <t>Cerrillos</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>487496.72</v>
+          <t>Cerro Navia</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>962259.6899999999</v>
+          <t>Vitacura</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>848713.38</v>
+          <t>Conchalí</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lo Espejo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>271989.5</v>
+          <t>El Bosque</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lo Prado</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>303825.31</v>
+          <t>Estación Central</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Macul</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>505286.38</v>
+          <t>La Florida</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Maipú</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>446942.47</v>
+          <t>La Granja</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>María Pinto</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>295409.34</v>
+          <t>La Pintana</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Melipilla</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>288901.03</v>
+          <t>Las Condes</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>856031.5600000001</v>
+          <t>Lo Barnechea</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Padre Hurtado</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>451923.09</v>
+          <t>Lo Espejo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paine</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>317556.84</v>
+          <t>Lo Prado</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pedro Aguirre Cerda</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>286410.47</v>
+          <t>Macul</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>403801.47</v>
+          <t>Maipú</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>461524.31</v>
+          <t>Ñuñoa</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pirque</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>416749.75</v>
+          <t>Pedro Aguirre Cerda</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>967753.8100000001</v>
+          <t>Pudahuel</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pudahuel</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>405932.75</v>
+          <t>Quilicura</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>408933.69</v>
+          <t>Quinta Normal</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quilicura</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>459116.5</v>
+          <t>Recoleta</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quinta Normal</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>371511.12</v>
+          <t>Renca</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Recoleta</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>335464.53</v>
+          <t>El Monte</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Renca</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>335872.31</v>
+          <t>Padre Hurtado</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>364957.44</v>
+          <t>Peñaflor</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>334567.12</v>
+          <t>Talagante</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>San José de Maipo</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>369292.28</v>
+          <t>Paine</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>653121.0600000001</v>
+          <t>Isla de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>San Pedro</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>223357.52</v>
+          <t>Buin</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>San Ramón</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>267090.22</v>
+          <t>San José de Maipo</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>558202.0600000001</v>
+          <t>Tiltil</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Talagante</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>382117.84</v>
+          <t>Melipilla</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Tiltil</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>520258.03</v>
+          <t>San Pedro</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vitacura</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>1015543.88</v>
+          <t>Alhué</t>
+        </is>
       </c>
     </row>
   </sheetData>
